--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="G2">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H3">
         <v>426</v>
